--- a/Policy_dictionairy.xlsx
+++ b/Policy_dictionairy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\policy-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D073566A-8792-4E38-AF5C-1CCDCA2B24A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAD05FE-CC0E-47CD-815B-02E2E7E86514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="-4695" windowWidth="16410" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="911">
   <si>
     <t>WERKGELEGENHEID*</t>
   </si>
@@ -721,9 +721,6 @@
   </si>
   <si>
     <t>TERREUR*</t>
-  </si>
-  <si>
-    <t>buitenlandse_handel</t>
   </si>
   <si>
     <t>EMBARGO*</t>
@@ -3037,10 +3034,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B1" t="s">
         <v>910</v>
-      </c>
-      <c r="B1" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3064,7 +3061,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3072,7 +3069,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3080,7 +3077,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3112,7 +3109,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3120,7 +3117,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3128,7 +3125,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3144,7 +3141,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3152,7 +3149,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3168,7 +3165,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3176,7 +3173,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3184,7 +3181,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3192,7 +3189,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3200,7 +3197,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3208,7 +3205,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3224,7 +3221,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3240,7 +3237,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3248,7 +3245,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3256,7 +3253,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3280,7 +3277,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3288,7 +3285,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3296,7 +3293,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3304,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3312,7 +3309,7 @@
         <v>2</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3320,7 +3317,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3328,7 +3325,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3336,7 +3333,7 @@
         <v>2</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3344,7 +3341,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3352,7 +3349,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3360,7 +3357,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3368,7 +3365,7 @@
         <v>2</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3376,7 +3373,7 @@
         <v>2</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3384,7 +3381,7 @@
         <v>2</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3392,7 +3389,7 @@
         <v>2</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3400,7 +3397,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3408,7 +3405,7 @@
         <v>2</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3424,7 +3421,7 @@
         <v>2</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3432,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3440,7 +3437,7 @@
         <v>2</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3448,7 +3445,7 @@
         <v>2</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3456,7 +3453,7 @@
         <v>2</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3472,7 +3469,7 @@
         <v>2</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3480,7 +3477,7 @@
         <v>2</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3488,7 +3485,7 @@
         <v>2</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3496,7 +3493,7 @@
         <v>2</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3504,7 +3501,7 @@
         <v>2</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3512,7 +3509,7 @@
         <v>2</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3520,7 +3517,7 @@
         <v>2</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3528,7 +3525,7 @@
         <v>2</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3552,7 +3549,7 @@
         <v>2</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3560,7 +3557,7 @@
         <v>2</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3576,7 +3573,7 @@
         <v>2</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3584,7 +3581,7 @@
         <v>2</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3592,7 +3589,7 @@
         <v>2</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3600,7 +3597,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3608,7 +3605,7 @@
         <v>2</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3616,7 +3613,7 @@
         <v>2</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3624,7 +3621,7 @@
         <v>2</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3632,7 +3629,7 @@
         <v>2</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3640,7 +3637,7 @@
         <v>2</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3648,7 +3645,7 @@
         <v>2</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3680,7 +3677,7 @@
         <v>19</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3688,7 +3685,7 @@
         <v>19</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3704,7 +3701,7 @@
         <v>19</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3712,7 +3709,7 @@
         <v>19</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3720,7 +3717,7 @@
         <v>19</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3728,7 +3725,7 @@
         <v>19</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3736,7 +3733,7 @@
         <v>19</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3744,7 +3741,7 @@
         <v>19</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3752,7 +3749,7 @@
         <v>19</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3760,7 +3757,7 @@
         <v>19</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3768,7 +3765,7 @@
         <v>19</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3776,7 +3773,7 @@
         <v>19</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3784,7 +3781,7 @@
         <v>19</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3792,7 +3789,7 @@
         <v>19</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3800,7 +3797,7 @@
         <v>19</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3808,7 +3805,7 @@
         <v>19</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3824,7 +3821,7 @@
         <v>19</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3832,7 +3829,7 @@
         <v>19</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3848,7 +3845,7 @@
         <v>19</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3856,7 +3853,7 @@
         <v>19</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3880,7 +3877,7 @@
         <v>19</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3888,7 +3885,7 @@
         <v>19</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3896,7 +3893,7 @@
         <v>19</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3912,7 +3909,7 @@
         <v>19</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3920,7 +3917,7 @@
         <v>19</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3928,7 +3925,7 @@
         <v>19</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3936,7 +3933,7 @@
         <v>19</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3944,7 +3941,7 @@
         <v>19</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3952,7 +3949,7 @@
         <v>19</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3960,7 +3957,7 @@
         <v>19</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3968,7 +3965,7 @@
         <v>19</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3976,7 +3973,7 @@
         <v>19</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3984,7 +3981,7 @@
         <v>19</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -3992,7 +3989,7 @@
         <v>19</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4008,7 +4005,7 @@
         <v>19</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4024,7 +4021,7 @@
         <v>19</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4032,7 +4029,7 @@
         <v>19</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4040,7 +4037,7 @@
         <v>19</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4048,7 +4045,7 @@
         <v>19</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4056,7 +4053,7 @@
         <v>19</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4064,7 +4061,7 @@
         <v>19</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4072,7 +4069,7 @@
         <v>19</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4080,7 +4077,7 @@
         <v>19</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4088,7 +4085,7 @@
         <v>19</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4096,7 +4093,7 @@
         <v>19</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4104,7 +4101,7 @@
         <v>19</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4112,7 +4109,7 @@
         <v>19</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4120,7 +4117,7 @@
         <v>19</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4128,7 +4125,7 @@
         <v>19</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4136,7 +4133,7 @@
         <v>19</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4144,7 +4141,7 @@
         <v>19</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4152,7 +4149,7 @@
         <v>19</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4160,7 +4157,7 @@
         <v>19</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4168,7 +4165,7 @@
         <v>19</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4184,7 +4181,7 @@
         <v>19</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4192,7 +4189,7 @@
         <v>19</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4208,7 +4205,7 @@
         <v>19</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4216,7 +4213,7 @@
         <v>19</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4224,7 +4221,7 @@
         <v>19</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4232,7 +4229,7 @@
         <v>19</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4240,7 +4237,7 @@
         <v>19</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4248,7 +4245,7 @@
         <v>19</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4256,7 +4253,7 @@
         <v>19</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4264,7 +4261,7 @@
         <v>19</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4272,7 +4269,7 @@
         <v>19</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4280,7 +4277,7 @@
         <v>19</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4288,7 +4285,7 @@
         <v>19</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4304,7 +4301,7 @@
         <v>19</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4312,7 +4309,7 @@
         <v>19</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4320,7 +4317,7 @@
         <v>19</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4336,7 +4333,7 @@
         <v>19</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4504,7 +4501,7 @@
         <v>36</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4512,7 +4509,7 @@
         <v>36</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4520,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4528,7 +4525,7 @@
         <v>36</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4536,7 +4533,7 @@
         <v>36</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4544,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4552,7 +4549,7 @@
         <v>36</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4560,7 +4557,7 @@
         <v>36</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4568,7 +4565,7 @@
         <v>36</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4576,7 +4573,7 @@
         <v>36</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4584,7 +4581,7 @@
         <v>36</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4592,7 +4589,7 @@
         <v>36</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4600,7 +4597,7 @@
         <v>36</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4608,7 +4605,7 @@
         <v>36</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4616,7 +4613,7 @@
         <v>36</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4624,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4640,7 +4637,7 @@
         <v>36</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4648,7 +4645,7 @@
         <v>36</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4664,7 +4661,7 @@
         <v>36</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4672,7 +4669,7 @@
         <v>36</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4680,7 +4677,7 @@
         <v>36</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4688,7 +4685,7 @@
         <v>36</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4704,7 +4701,7 @@
         <v>36</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4712,7 +4709,7 @@
         <v>36</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4720,7 +4717,7 @@
         <v>36</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4744,7 +4741,7 @@
         <v>36</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4752,7 +4749,7 @@
         <v>36</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4760,7 +4757,7 @@
         <v>36</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4776,7 +4773,7 @@
         <v>36</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4800,7 +4797,7 @@
         <v>64</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4808,7 +4805,7 @@
         <v>64</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4816,7 +4813,7 @@
         <v>64</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4824,7 +4821,7 @@
         <v>64</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4832,7 +4829,7 @@
         <v>64</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -4840,7 +4837,7 @@
         <v>64</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5008,7 +5005,7 @@
         <v>64</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5032,7 +5029,7 @@
         <v>64</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5040,7 +5037,7 @@
         <v>64</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5048,7 +5045,7 @@
         <v>64</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5056,7 +5053,7 @@
         <v>64</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5064,7 +5061,7 @@
         <v>64</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5072,7 +5069,7 @@
         <v>64</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5088,7 +5085,7 @@
         <v>64</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5424,7 +5421,7 @@
         <v>89</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="300" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5552,7 +5549,7 @@
         <v>89</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="316" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5560,7 +5557,7 @@
         <v>89</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="317" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5568,7 +5565,7 @@
         <v>89</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="318" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5576,7 +5573,7 @@
         <v>89</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="319" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5584,7 +5581,7 @@
         <v>89</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="320" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5592,7 +5589,7 @@
         <v>89</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="321" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5600,7 +5597,7 @@
         <v>89</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="322" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5608,7 +5605,7 @@
         <v>89</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5616,7 +5613,7 @@
         <v>145</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="324" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5624,7 +5621,7 @@
         <v>145</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="325" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5632,7 +5629,7 @@
         <v>145</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="326" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5640,7 +5637,7 @@
         <v>145</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="327" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5648,7 +5645,7 @@
         <v>145</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="328" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5680,7 +5677,7 @@
         <v>145</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="332" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5888,7 +5885,7 @@
         <v>145</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="358" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5952,7 +5949,7 @@
         <v>181</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="366" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5968,7 +5965,7 @@
         <v>181</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="368" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5976,7 +5973,7 @@
         <v>181</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="369" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5984,7 +5981,7 @@
         <v>181</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="370" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -5992,7 +5989,7 @@
         <v>181</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="371" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6008,7 +6005,7 @@
         <v>181</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6024,7 +6021,7 @@
         <v>181</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="375" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6040,7 +6037,7 @@
         <v>181</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="377" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6048,7 +6045,7 @@
         <v>181</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="378" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6064,7 +6061,7 @@
         <v>181</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="380" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6072,7 +6069,7 @@
         <v>181</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6080,7 +6077,7 @@
         <v>181</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="382" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6088,7 +6085,7 @@
         <v>181</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6096,7 +6093,7 @@
         <v>181</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6104,7 +6101,7 @@
         <v>181</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="385" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6112,7 +6109,7 @@
         <v>181</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="386" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6120,7 +6117,7 @@
         <v>181</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="387" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6128,7 +6125,7 @@
         <v>181</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="388" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6136,7 +6133,7 @@
         <v>181</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="389" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6144,7 +6141,7 @@
         <v>181</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="390" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6152,7 +6149,7 @@
         <v>181</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="391" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6192,7 +6189,7 @@
         <v>181</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="396" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6200,7 +6197,7 @@
         <v>181</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="397" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6208,7 +6205,7 @@
         <v>181</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="398" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6216,7 +6213,7 @@
         <v>181</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6232,7 +6229,7 @@
         <v>181</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="401" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6240,7 +6237,7 @@
         <v>181</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6248,7 +6245,7 @@
         <v>181</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="403" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6256,7 +6253,7 @@
         <v>181</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="404" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6264,7 +6261,7 @@
         <v>181</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="405" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6272,7 +6269,7 @@
         <v>181</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="406" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6280,7 +6277,7 @@
         <v>181</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="407" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6288,7 +6285,7 @@
         <v>181</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6296,7 +6293,7 @@
         <v>181</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="409" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6320,7 +6317,7 @@
         <v>181</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="412" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6328,7 +6325,7 @@
         <v>181</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="413" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6336,7 +6333,7 @@
         <v>181</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="414" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6344,7 +6341,7 @@
         <v>181</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6352,7 +6349,7 @@
         <v>181</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="416" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6360,7 +6357,7 @@
         <v>181</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="417" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6376,7 +6373,7 @@
         <v>181</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="419" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6384,7 +6381,7 @@
         <v>181</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="420" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6408,7 +6405,7 @@
         <v>181</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="423" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6416,7 +6413,7 @@
         <v>181</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="424" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6424,7 +6421,7 @@
         <v>181</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="425" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6432,7 +6429,7 @@
         <v>181</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="426" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6440,7 +6437,7 @@
         <v>181</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="427" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6448,7 +6445,7 @@
         <v>181</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="428" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6456,7 +6453,7 @@
         <v>181</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="429" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6464,7 +6461,7 @@
         <v>181</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="430" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6472,7 +6469,7 @@
         <v>181</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="431" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6480,7 +6477,7 @@
         <v>181</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="432" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6488,7 +6485,7 @@
         <v>181</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="433" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6496,7 +6493,7 @@
         <v>181</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6504,7 +6501,7 @@
         <v>181</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="435" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6512,7 +6509,7 @@
         <v>181</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="436" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6520,7 +6517,7 @@
         <v>181</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="437" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6528,7 +6525,7 @@
         <v>181</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6536,7 +6533,7 @@
         <v>181</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="439" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6552,7 +6549,7 @@
         <v>181</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="441" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6560,7 +6557,7 @@
         <v>181</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="442" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6576,7 +6573,7 @@
         <v>181</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6584,7 +6581,7 @@
         <v>181</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="445" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6592,7 +6589,7 @@
         <v>181</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6600,7 +6597,7 @@
         <v>181</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6608,7 +6605,7 @@
         <v>181</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="448" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6616,7 +6613,7 @@
         <v>181</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="449" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6624,7 +6621,7 @@
         <v>181</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="450" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6632,7 +6629,7 @@
         <v>181</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="451" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6640,7 +6637,7 @@
         <v>181</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="452" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6648,7 +6645,7 @@
         <v>181</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="453" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6656,7 +6653,7 @@
         <v>181</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="454" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6664,7 +6661,7 @@
         <v>181</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="455" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6680,7 +6677,7 @@
         <v>181</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="457" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6688,7 +6685,7 @@
         <v>181</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="458" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6696,7 +6693,7 @@
         <v>181</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="459" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6712,7 +6709,7 @@
         <v>181</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="461" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6720,7 +6717,7 @@
         <v>181</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="462" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6728,7 +6725,7 @@
         <v>181</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="463" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6736,7 +6733,7 @@
         <v>181</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="464" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6744,7 +6741,7 @@
         <v>181</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="465" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6752,7 +6749,7 @@
         <v>181</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="466" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6760,7 +6757,7 @@
         <v>199</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="467" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6768,7 +6765,7 @@
         <v>199</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="468" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6776,7 +6773,7 @@
         <v>199</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="469" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6784,7 +6781,7 @@
         <v>199</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="470" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6800,7 +6797,7 @@
         <v>199</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="472" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6808,7 +6805,7 @@
         <v>199</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="473" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6816,7 +6813,7 @@
         <v>199</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="474" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6824,7 +6821,7 @@
         <v>199</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="475" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6832,7 +6829,7 @@
         <v>199</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="476" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6840,7 +6837,7 @@
         <v>199</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="477" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6848,7 +6845,7 @@
         <v>199</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="478" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6856,7 +6853,7 @@
         <v>199</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="479" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6864,7 +6861,7 @@
         <v>199</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="480" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6872,7 +6869,7 @@
         <v>199</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="481" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6888,7 +6885,7 @@
         <v>199</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="483" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6896,7 +6893,7 @@
         <v>199</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="484" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6904,7 +6901,7 @@
         <v>199</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="485" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6912,7 +6909,7 @@
         <v>199</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="486" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6920,7 +6917,7 @@
         <v>199</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="487" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6928,7 +6925,7 @@
         <v>199</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="488" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6936,7 +6933,7 @@
         <v>199</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="489" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6944,7 +6941,7 @@
         <v>199</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="490" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6952,7 +6949,7 @@
         <v>199</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="491" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6960,7 +6957,7 @@
         <v>199</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="492" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6968,7 +6965,7 @@
         <v>199</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="493" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -6992,7 +6989,7 @@
         <v>199</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="496" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7008,7 +7005,7 @@
         <v>199</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="498" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7016,7 +7013,7 @@
         <v>199</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="499" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7024,7 +7021,7 @@
         <v>199</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="500" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7040,7 +7037,7 @@
         <v>199</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="502" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7048,7 +7045,7 @@
         <v>199</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="503" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7064,7 +7061,7 @@
         <v>199</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="505" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7072,7 +7069,7 @@
         <v>199</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="506" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7088,7 +7085,7 @@
         <v>199</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="508" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7112,7 +7109,7 @@
         <v>199</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="511" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
@@ -7120,12 +7117,12 @@
         <v>199</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="512" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>213</v>
@@ -7133,15 +7130,15 @@
     </row>
     <row r="513" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B513" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="B513" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="514" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>208</v>
@@ -7149,7 +7146,7 @@
     </row>
     <row r="515" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>209</v>
@@ -7157,7 +7154,7 @@
     </row>
     <row r="516" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>210</v>
@@ -7165,7 +7162,7 @@
     </row>
     <row r="517" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>211</v>
@@ -7173,7 +7170,7 @@
     </row>
     <row r="518" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>212</v>
@@ -7181,7 +7178,7 @@
     </row>
     <row r="519" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>214</v>
@@ -7189,7 +7186,7 @@
     </row>
     <row r="520" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>215</v>
@@ -7197,7 +7194,7 @@
     </row>
     <row r="521" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>216</v>
@@ -7205,7 +7202,7 @@
     </row>
     <row r="522" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>217</v>
@@ -7213,7 +7210,7 @@
     </row>
     <row r="523" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>218</v>
@@ -7221,7 +7218,7 @@
     </row>
     <row r="524" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>219</v>
@@ -7229,7 +7226,7 @@
     </row>
     <row r="525" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>220</v>
@@ -7237,7 +7234,7 @@
     </row>
     <row r="526" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>221</v>
@@ -7245,7 +7242,7 @@
     </row>
     <row r="527" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>222</v>
@@ -7253,7 +7250,7 @@
     </row>
     <row r="528" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>223</v>
@@ -7261,7 +7258,7 @@
     </row>
     <row r="529" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>224</v>
@@ -7269,7 +7266,7 @@
     </row>
     <row r="530" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>225</v>
@@ -7277,7 +7274,7 @@
     </row>
     <row r="531" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>226</v>
@@ -7285,55 +7282,55 @@
     </row>
     <row r="532" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="533" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="534" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="535" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="536" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="537" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="538" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>137</v>
@@ -7341,7 +7338,7 @@
     </row>
     <row r="539" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>227</v>
@@ -7349,7 +7346,7 @@
     </row>
     <row r="540" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>228</v>
@@ -7357,31 +7354,31 @@
     </row>
     <row r="541" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="542" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="543" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="544" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>229</v>
@@ -7389,527 +7386,527 @@
     </row>
     <row r="545" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="546" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="547" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="548" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="549" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="550" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B550" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B550" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="551" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="552" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="553" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="554" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="555" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="556" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="557" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="558" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="559" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="560" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="561" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="562" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="563" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="564" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="565" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="566" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="567" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="568" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="569" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="570" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="571" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="573" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="574" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="575" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="576" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="577" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="578" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="579" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="580" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="581" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="582" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="583" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="584" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="585" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="586" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="587" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="588" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="589" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="590" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="591" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="592" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="593" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="594" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="595" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="596" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="597" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="598" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="599" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="600" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="601" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="602" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="603" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="604" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="605" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="606" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="607" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="608" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="609" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="610" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>231</v>
@@ -7917,751 +7914,751 @@
     </row>
     <row r="611" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="612" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="613" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="614" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="615" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="616" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="617" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="618" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="619" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="620" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="621" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="622" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="623" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="624" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="625" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="626" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="627" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="628" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="629" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="630" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="631" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="632" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="633" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="634" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="635" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="636" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B636" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="B636" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="637" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="638" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="639" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="640" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="641" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="642" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="643" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="644" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="645" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="646" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="647" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="648" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="649" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="650" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="651" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="652" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="653" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="654" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="655" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="656" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="657" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="658" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="659" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="660" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="661" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="662" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="663" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="664" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="665" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="666" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="667" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="668" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="669" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="670" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="671" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="672" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="673" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="674" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="675" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="676" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="677" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="678" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="679" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="680" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="681" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="682" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="683" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="684" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="685" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="686" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="687" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="688" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="689" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="690" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="691" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="692" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="693" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="694" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="695" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="696" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="697" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="698" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="699" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="700" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="701" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="702" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="703" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="704" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B704" s="2" t="s">
         <v>14</v>
@@ -8669,103 +8666,103 @@
     </row>
     <row r="705" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="706" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="707" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="708" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="709" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="710" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="711" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="712" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="713" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="714" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="715" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="716" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="717" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B717" s="2" t="s">
         <v>17</v>
@@ -8773,407 +8770,407 @@
     </row>
     <row r="718" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="719" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="720" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="721" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="722" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="723" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="724" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="725" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="726" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="727" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="728" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="729" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="730" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="731" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="732" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="733" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="734" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="735" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="736" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="737" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="738" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="739" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="740" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="741" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="742" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="743" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="744" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="745" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="746" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="747" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="748" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="749" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="750" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="751" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="752" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="753" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="754" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="755" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="756" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="757" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="758" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="759" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="760" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="761" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="762" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="763" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="764" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="765" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="766" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="767" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="768" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B768" s="2" t="s">
         <v>230</v>
@@ -9181,1088 +9178,1088 @@
     </row>
     <row r="769" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="770" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="771" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="772" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="773" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="774" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="775" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="776" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="777" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="778" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="779" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="780" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="781" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="782" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="783" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="784" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="785" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="786" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="787" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="788" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A788" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="789" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A789" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="790" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A790" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="791" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A791" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="792" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A792" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="793" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A793" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="794" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A794" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="795" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A795" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="796" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A796" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="797" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A797" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="798" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A798" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="799" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A799" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="800" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A800" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="801" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A801" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="802" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A802" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="803" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A803" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="804" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A804" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="805" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A805" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="806" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A806" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="807" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A807" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B807" s="2" t="s">
         <v>881</v>
-      </c>
-      <c r="B807" s="2" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="808" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A808" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="809" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A809" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="810" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A810" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="811" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A811" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="812" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A812" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="813" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A813" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="814" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A814" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="815" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A815" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="816" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A816" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="817" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A817" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B817" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="818" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A818" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="819" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A819" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B819" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="820" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A820" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="821" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A821" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="822" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A822" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="823" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A823" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="824" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A824" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="825" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A825" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="826" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A826" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B826" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="827" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A827" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B827" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="828" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A828" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B828" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="829" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A829" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="830" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A830" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B830" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="831" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A831" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B831" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="832" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A832" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B832" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="833" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A833" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B833" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="834" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A834" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B834" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="835" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A835" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B835" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="836" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A836" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B836" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="837" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A837" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B837" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="838" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A838" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B838" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="839" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A839" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B839" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="840" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B840" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="841" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B841" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="842" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B842" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="843" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B843" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="844" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B844" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="845" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B845" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="846" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B846" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="847" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B847" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="848" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B848" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="B848" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="849" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B849" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="850" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B850" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="851" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B851" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="852" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B852" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="853" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A853" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B853" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="854" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A854" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="855" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A855" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="856" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A856" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B856" s="1"/>
     </row>
     <row r="857" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A857" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B857" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="858" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A858" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B858" s="2" t="s">
         <v>904</v>
-      </c>
-      <c r="B858" s="2" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="859" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A859" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B859" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="860" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A860" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B860" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="861" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A861" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B861" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="862" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A862" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B862" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="863" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A863" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B863" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="864" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A864" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="865" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A865" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="866" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A866" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="867" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A867" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B867" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="868" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A868" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B868" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="869" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A869" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B869" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="870" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A870" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B870" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="871" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A871" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B871" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="872" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A872" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B872" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="873" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A873" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B873" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="874" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A874" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B874" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="875" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A875" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B875" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="876" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A876" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B876" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="877" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A877" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B877" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="878" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A878" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B878" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="879" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A879" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B879" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="880" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A880" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B880" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="881" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A881" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B881" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="882" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A882" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B882" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="883" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A883" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B883" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="884" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A884" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B884" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="885" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A885" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B885" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="886" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A886" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B886" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="887" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A887" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B887" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="888" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A888" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B888" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="889" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A889" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B889" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="890" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A890" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B890" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="891" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A891" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B891" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="892" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A892" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B892" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="893" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A893" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B893" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="894" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A894" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B894" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="895" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A895" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B895" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="896" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A896" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B896" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="897" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A897" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B897" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="898" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A898" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B898" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="899" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A899" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B899" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="900" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A900" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B900" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="901" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A901" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B901" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="902" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A902" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B902" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="903" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A903" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B903" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="904" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A904" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B904" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="905" spans="1:2" ht="12.75" x14ac:dyDescent="0.2">
